--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/машины ПОКОМ ЗПФ.xlsx
@@ -1,37 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D378A893-6703-41A2-8D8A-36CAEBE59A6D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E7C5B2-D7E1-4888-BEEB-1EF9811E21E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Бердянск</t>
   </si>
@@ -94,6 +88,9 @@
   </si>
   <si>
     <t>30,06,</t>
+  </si>
+  <si>
+    <t>отмена</t>
   </si>
 </sst>
 </file>
@@ -124,7 +121,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -149,6 +146,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -562,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -594,6 +597,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -913,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -928,47 +936,47 @@
     <col min="14" max="15" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="41" t="s">
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="41" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="41" t="s">
+      <c r="I1" s="47"/>
+      <c r="J1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="41" t="s">
+      <c r="K1" s="48"/>
+      <c r="L1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="35" t="s">
+      <c r="M1" s="48"/>
+      <c r="N1" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="36" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="34"/>
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="43"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
@@ -999,31 +1007,31 @@
       <c r="M2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="36"/>
-      <c r="O2" s="32"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="37"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="19">
-        <v>11784</v>
+        <v>7253</v>
       </c>
       <c r="C3" s="20">
-        <v>32</v>
-      </c>
-      <c r="D3" s="4">
-        <v>11784</v>
-      </c>
-      <c r="E3" s="5">
-        <v>32</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
       <c r="F3" s="4"/>
       <c r="G3" s="5"/>
       <c r="H3" s="4"/>
       <c r="I3" s="6"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="6"/>
+      <c r="J3" s="19">
+        <v>7253</v>
+      </c>
+      <c r="K3" s="20">
+        <v>20</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="6"/>
       <c r="N3" s="4">
@@ -1035,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>2</v>
       </c>
@@ -1101,14 +1109,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="32">
         <v>6328</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="33">
         <v>17</v>
       </c>
       <c r="D6" s="2"/>
@@ -1117,24 +1125,23 @@
       <c r="G6" s="3"/>
       <c r="H6" s="2"/>
       <c r="I6" s="7"/>
-      <c r="J6" s="2">
-        <v>6328</v>
-      </c>
-      <c r="K6" s="7">
-        <v>17</v>
-      </c>
+      <c r="J6" s="31"/>
+      <c r="K6" s="34"/>
       <c r="L6" s="2"/>
       <c r="M6" s="7"/>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6328</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="P6" s="35" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
         <v>12</v>
       </c>
@@ -1167,7 +1174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>18</v>
       </c>
@@ -1200,7 +1207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>13</v>
       </c>
@@ -1233,25 +1240,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="21">
         <f t="shared" ref="B10:M10" si="2">SUM(B3:B9)</f>
-        <v>58727</v>
+        <v>54196</v>
       </c>
       <c r="C10" s="21">
         <f t="shared" si="2"/>
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="2"/>
-        <v>11784</v>
+        <v>0</v>
       </c>
       <c r="E10" s="16">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="2"/>
@@ -1271,11 +1278,11 @@
       </c>
       <c r="J10" s="15">
         <f t="shared" si="2"/>
-        <v>11270</v>
+        <v>12195</v>
       </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L10" s="15">
         <f t="shared" si="2"/>
@@ -1287,14 +1294,14 @@
       </c>
       <c r="N10" s="28">
         <f t="shared" ref="N10" si="3">B10-D10-F10-H10-L10</f>
-        <v>11270</v>
+        <v>18523</v>
       </c>
       <c r="O10" s="29">
         <f>C10-E10-G10-I10-M10</f>
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
         <v>19</v>
       </c>
